--- a/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Total Δ⁹-THC</t>
+          <t>Total Δ⁹-THC % w/w</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -634,7 +634,7 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>21.80%</t>
+          <t>21.80</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -669,7 +669,7 @@
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26.14 %w/w (U 1.61)</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="C9" s="18" t="inlineStr"/>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>21.03%</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="10">
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>25.01 %w/w (U 1.54)</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>23.42%</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="D12" s="28" t="inlineStr">
         <is>
-          <t>20.39%</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
@@ -887,7 +887,7 @@
       <c r="C14" s="9" t="inlineStr"/>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>23.00%</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>20.29%</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="16">
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>24.05 %w/w (U 1.48)</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>14.93%</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>23.70%</t>
+          <t>23.70</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>17.22%</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="21">
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>18.67 %w/w (U 1.15)</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>15.95%</t>
+          <t>15.95</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -1224,7 +1224,7 @@
       <c r="C23" s="22" t="inlineStr"/>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>15.35%</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       <c r="C24" s="26" t="inlineStr"/>
       <c r="D24" s="28" t="inlineStr">
         <is>
-          <t>17.94%</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>20.79%</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>23.19%</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -1386,7 +1386,7 @@
     <row r="28">
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>22.61 %w/w (U 1.39)</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>25.45%</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>18.98%</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="31">
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>18.52 %w/w (U 1.14)</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>24.89%</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>21.36%</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>19.81%</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>21.29%</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>14.83%</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="37">
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>15.70% w/w (U 0.96% w/w)</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>25.73%</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>18.67%</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D41" s="28" t="inlineStr">
         <is>
-          <t>16.82%</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>15.38%</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>18.27%</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -2036,7 +2036,7 @@
     <row r="45">
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>18.04 %w/w (U 1.11)</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>16.55%</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>14.16%</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -2212,7 +2212,7 @@
       <c r="C49" s="9" t="inlineStr"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -2253,7 +2253,7 @@
       <c r="C50" s="15" t="inlineStr"/>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>8.09 %w/w (U ±0.50)</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>22.43%</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="E52" s="21" t="inlineStr">
@@ -2337,7 +2337,7 @@
     <row r="53">
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>21.61 %w/w (U 1.33)</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>20.39%</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>16.56%</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="57">
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>18.91% w/w (U 1.16% w/w)</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>21.51%</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>22.11%</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="E60" s="21" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D61" s="28" t="inlineStr">
         <is>
-          <t>21.67%</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="E61" s="29" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>10.01%</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>14.06%</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -2737,7 +2737,7 @@
     <row r="65">
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>12.25% w/w (U 0.75% w/w)</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -2778,7 +2778,7 @@
       <c r="C66" s="15" t="inlineStr"/>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>13.33%</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D68" s="28" t="inlineStr">
         <is>
-          <t>8.02%</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>24.96%</t>
+          <t>24.96</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>20.84%</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -2959,7 +2959,7 @@
     <row r="72">
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>18.29% w/w (U 1.12% w/w)</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>22.30%</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D75" s="28" t="inlineStr">
         <is>
-          <t>16.93%</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>10.96%</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -3149,7 +3149,7 @@
       <c r="C78" s="9" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>11.20 %w/w (U ±0.69)</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -3190,7 +3190,7 @@
       <c r="C79" s="15" t="inlineStr"/>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>9.20 %w/w (U ±0.57)</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -3238,7 +3238,7 @@
       <c r="C81" s="26" t="inlineStr"/>
       <c r="D81" s="28" t="inlineStr">
         <is>
-          <t>11.53 %w/w (U ±0.71)</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="E81" s="29" t="inlineStr">
@@ -3286,7 +3286,7 @@
       <c r="C83" s="9" t="inlineStr"/>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>19.14 %w/w (U ±1.18)</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -3327,7 +3327,7 @@
       <c r="C84" s="5" t="inlineStr"/>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>25.27 %w/w (U ±1.55)</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="85">
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>20.21 %w/w (U ±1.24)</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -3400,7 +3400,7 @@
       <c r="C86" s="5" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>19.84 %w/w (U ±1.22)</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -3435,7 +3435,7 @@
       <c r="C87" s="12" t="n"/>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>21.84 %w/w (U ±1.34)</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
@@ -3483,7 +3483,7 @@
       <c r="C89" s="26" t="inlineStr"/>
       <c r="D89" s="28" t="inlineStr">
         <is>
-          <t>17.04 %w/w (U ±1.05)</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
@@ -3531,7 +3531,7 @@
       <c r="C91" s="15" t="inlineStr"/>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>13.35%</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr"/>
@@ -3575,7 +3575,7 @@
       <c r="C93" s="22" t="inlineStr"/>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>14.68%</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="E93" s="21" t="inlineStr"/>
@@ -3612,7 +3612,7 @@
       <c r="C94" s="22" t="inlineStr"/>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>16.69%</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="E94" s="21" t="inlineStr"/>
@@ -3649,7 +3649,7 @@
       <c r="C95" s="26" t="inlineStr"/>
       <c r="D95" s="28" t="inlineStr">
         <is>
-          <t>20.83%</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
@@ -3697,7 +3697,7 @@
       <c r="C97" s="9" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>18.16%</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr"/>
@@ -3734,7 +3734,7 @@
       <c r="C98" s="5" t="inlineStr"/>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>19.64%</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr"/>
@@ -3765,7 +3765,7 @@
       <c r="C99" s="12" t="n"/>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>13.93%</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
       <c r="C101" s="22" t="inlineStr"/>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>17.13%</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="E101" s="21" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
       <c r="C102" s="22" t="inlineStr"/>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>21.92%</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="E102" s="21" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="D103" s="28" t="inlineStr">
         <is>
-          <t>17.84 %w/w (U 1.10 %w/w, k=2)</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="E103" s="29" t="inlineStr">
@@ -3939,7 +3939,7 @@
       <c r="C105" s="9" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>18.29%</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -3980,7 +3980,7 @@
       <c r="C106" s="9" t="inlineStr"/>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>12.39%</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>18.86 %w/w (U 1.16 %w/w, k=2)</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
@@ -4073,7 +4073,7 @@
       <c r="C109" s="22" t="inlineStr"/>
       <c r="D109" s="20" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>17.59</t>
         </is>
       </c>
       <c r="E109" s="21" t="inlineStr">
@@ -4114,7 +4114,7 @@
       <c r="C110" s="22" t="inlineStr"/>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>18.98%</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="E110" s="21" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D111" s="28" t="inlineStr">
         <is>
-          <t>16.70 %w/w (U 1.03 %w/w, k=2)</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="E111" s="29" t="inlineStr">
@@ -4207,7 +4207,7 @@
       <c r="C113" s="9" t="inlineStr"/>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>20.54%</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -4248,7 +4248,7 @@
       <c r="C114" s="9" t="inlineStr"/>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>15.16%</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -4289,7 +4289,7 @@
       <c r="C115" s="9" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>18.58%</t>
+          <t>18.58</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>20.32 %w/w (U 1.25 %w/w, k=2)</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>26.32%</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="E118" s="21" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>25.72%</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="E119" s="21" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="D120" s="28" t="inlineStr">
         <is>
-          <t>24.78%</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="E120" s="29" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>17.32 %w/w (U 1.06 %w/w, k=2)</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>7.91 %w/w (U 0.49 %w/w, k=2)</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E124" s="21" t="inlineStr">
@@ -4621,7 +4621,7 @@
       <c r="C125" s="18" t="inlineStr"/>
       <c r="D125" s="20" t="inlineStr">
         <is>
-          <t>19.96%</t>
+          <t>19.96</t>
         </is>
       </c>
       <c r="E125" s="21" t="inlineStr">
@@ -4656,7 +4656,7 @@
       <c r="C126" s="12" t="n"/>
       <c r="D126" s="28" t="inlineStr">
         <is>
-          <t>20.03 %w/w (U 1.23 %w/w, k=2)</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="E126" s="29" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>17.67 %w/w (U 1.09 %w/w, k=2)</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="E128" s="14" t="inlineStr">
@@ -4756,7 +4756,7 @@
       <c r="C130" s="18" t="inlineStr"/>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>14.97%</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="E130" s="21" t="inlineStr">
@@ -4791,7 +4791,7 @@
       <c r="C131" s="12" t="n"/>
       <c r="D131" s="28" t="inlineStr">
         <is>
-          <t>17.31 %w/w (U 1.06 %w/w, k=2)</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="E131" s="29" t="inlineStr">

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
@@ -1942,6 +1942,11 @@
           <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
@@ -4979,74 +4984,75 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
@@ -10,7 +10,7 @@
     <sheet name="THC by Strain" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'THC by Strain'!$A$4:$I$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'THC by Strain'!$A$4:$I$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1688,7 +1688,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Cup Junky      4 batch(es)      Total Δ⁹-THC across batches: 14.93 – 24.05 %</t>
+          <t xml:space="preserve">   Cap Junky      9 batch(es)      Total Δ⁹-THC across batches: 14.93 – 24.96 %</t>
         </is>
       </c>
     </row>
@@ -1856,1302 +1856,1365 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="n">
+      <c r="A39" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>CJ062501/2</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>P050212</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>16.56</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>14.9 – 18.2 %</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>ППК25322</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>23.10.2025</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>18.91</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>197-4-К/26</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>CJ062501/1</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>P050222</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>21.51</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>n/a (informational)</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>ППК25321</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>23.10.2025</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>CJ072501</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>P050252</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>23.70</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>n/a (informational)</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>ППК25367</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>28.11.2025</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I39" s="18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>CJ082501/1</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>P060022</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>24.96</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>22.46 – 27.45 %</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>ППК26002</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>CJ082501/2</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>P060032</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>20.84</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>18.75 – 22.92 %</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>ППК26003</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>18.29</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>197-5-К/26</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>CJ092501</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>P060072</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>22.30</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>20.07 – 24.53 %</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>ППК26007</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Gorilla Glue      7 batch(es)      Total Δ⁹-THC across batches: 13.34 – 18.98 %</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="19" t="n">
+    <row r="48">
+      <c r="A48" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>GG1024</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr"/>
-      <c r="D41" s="21" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr"/>
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>13.34</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>12.6 – 15.4 %</t>
         </is>
       </c>
-      <c r="F41" s="19" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>n/a — Purely Plant in-house CoA (Batch GG1024, no certificate/report number printed)</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G48" s="19" t="inlineStr">
         <is>
           <t>23.04.2025</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="n">
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>GG1024_02</t>
         </is>
       </c>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>P050012</t>
         </is>
       </c>
-      <c r="D42" s="21" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
         <is>
           <t>15.95</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E49" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F42" s="19" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>ППК25140</t>
         </is>
       </c>
-      <c r="G42" s="19" t="inlineStr">
+      <c r="G49" s="19" t="inlineStr">
         <is>
           <t>22.05.2025</t>
         </is>
       </c>
-      <c r="H42" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="32" t="n">
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="B43" s="33" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>GG1024_01</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr">
+      <c r="C50" s="32" t="inlineStr">
         <is>
           <t>P050092</t>
         </is>
       </c>
-      <c r="D43" s="21" t="inlineStr">
+      <c r="D50" s="21" t="inlineStr">
         <is>
           <t>17.22</t>
         </is>
       </c>
-      <c r="E43" s="22" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>ППК25104</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>17.04.2025</t>
         </is>
       </c>
-      <c r="H43" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I43" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="D44" s="21" t="inlineStr">
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" s="21" t="inlineStr">
         <is>
           <t>18.67</t>
         </is>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F44" s="19" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>197-9-К/26</t>
         </is>
       </c>
-      <c r="G44" s="19" t="inlineStr">
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H44" s="23" t="inlineStr">
+      <c r="H51" s="23" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="n">
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="n">
         <v>54</v>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>GG112501</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>P060252</t>
         </is>
       </c>
-      <c r="D45" s="21" t="inlineStr">
+      <c r="D52" s="21" t="inlineStr">
         <is>
           <t>17.94</t>
         </is>
       </c>
-      <c r="E45" s="22" t="inlineStr"/>
-      <c r="F45" s="19" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr"/>
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>ППК26061</t>
         </is>
       </c>
-      <c r="G45" s="19" t="inlineStr">
+      <c r="G52" s="19" t="inlineStr">
         <is>
           <t>11.05.2026</t>
         </is>
       </c>
-      <c r="H45" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I45" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="n">
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="n">
         <v>61</v>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>GG012601</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>P060302</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
+      <c r="D53" s="21" t="inlineStr">
         <is>
           <t>15.35</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr"/>
-      <c r="F46" s="19" t="inlineStr">
+      <c r="E53" s="22" t="inlineStr"/>
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>ППК26062</t>
         </is>
       </c>
-      <c r="G46" s="19" t="inlineStr">
+      <c r="G53" s="19" t="inlineStr">
         <is>
           <t>11.05.2026</t>
         </is>
       </c>
-      <c r="H46" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="32" t="n">
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="n">
         <v>68</v>
       </c>
-      <c r="B47" s="33" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>GG012603</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
         <is>
           <t>P060402</t>
         </is>
       </c>
-      <c r="D47" s="21" t="inlineStr">
+      <c r="D54" s="21" t="inlineStr">
         <is>
           <t>17.59</t>
         </is>
       </c>
-      <c r="E47" s="22" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
+      <c r="F54" s="19" t="inlineStr">
         <is>
           <t>ППК26114</t>
         </is>
       </c>
-      <c r="G47" s="19" t="inlineStr">
+      <c r="G54" s="19" t="inlineStr">
         <is>
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="H47" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I47" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="D48" s="21" t="inlineStr">
+      <c r="H54" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>16.70</t>
         </is>
       </c>
-      <c r="E48" s="22" t="inlineStr">
+      <c r="E55" s="22" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F48" s="19" t="inlineStr">
+      <c r="F55" s="19" t="inlineStr">
         <is>
           <t>197-8-К/26</t>
         </is>
       </c>
-      <c r="G48" s="19" t="inlineStr">
+      <c r="G55" s="19" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H48" s="23" t="inlineStr">
+      <c r="H55" s="23" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I48" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="25" t="n">
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="n">
         <v>74</v>
       </c>
-      <c r="B49" s="26" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>GG032601</t>
         </is>
       </c>
-      <c r="C49" s="25" t="inlineStr"/>
-      <c r="D49" s="27" t="inlineStr">
+      <c r="C56" s="25" t="inlineStr"/>
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>18.98</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E56" s="28" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F49" s="25" t="inlineStr">
+      <c r="F56" s="25" t="inlineStr">
         <is>
           <t>ППК26128</t>
         </is>
       </c>
-      <c r="G49" s="25" t="inlineStr">
+      <c r="G56" s="25" t="inlineStr">
         <is>
           <t>21.07.2026</t>
         </is>
       </c>
-      <c r="H49" s="29" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I49" s="30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="H56" s="29" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   High Pro Amnesia      3 batch(es)      Total Δ⁹-THC across batches: 14.97 – 22.43 %</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="n">
+    <row r="58">
+      <c r="A58" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>HPA1024</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>14.97</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>12.6 – 15.4 %</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>n/a — Purely Plant in-house CoA (Batch HPA1024, no certificate/report number printed)</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr">
         <is>
           <t>23.01.2025</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="D52" s="7" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>17.31</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>197-13-К/26</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>HPA1024_01</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>P050052</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>22.43</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>НИК22155</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
         <is>
           <t>24.06.2025</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="D54" s="7" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>21.61</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>197-14-К/26</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="n">
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>P050182</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="F62" s="13" t="inlineStr">
         <is>
           <t>ППК25278</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G62" s="13" t="inlineStr">
         <is>
           <t>19.09.2025</t>
         </is>
       </c>
-      <c r="H55" s="17" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Orange Punch Mimosa      8 batch(es)      Total Δ⁹-THC across batches: 7.91 – 20.03 %</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="32" t="n">
+    <row r="64">
+      <c r="A64" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="33" t="inlineStr">
+      <c r="B64" s="33" t="inlineStr">
         <is>
           <t>OPM1024</t>
         </is>
       </c>
-      <c r="C57" s="32" t="inlineStr"/>
-      <c r="D57" s="21" t="inlineStr">
+      <c r="C64" s="32" t="inlineStr"/>
+      <c r="D64" s="21" t="inlineStr">
         <is>
           <t>19.96</t>
         </is>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="E64" s="22" t="inlineStr">
         <is>
           <t>18.0 – 22.0 %</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>n/a — Purely Plant in-house CoA (Batch OPM1024, no certificate/report number printed)</t>
         </is>
       </c>
-      <c r="G57" s="19" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>23.04.2025</t>
         </is>
       </c>
-      <c r="H57" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I57" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="D58" s="21" t="inlineStr">
+      <c r="H64" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I64" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="D65" s="21" t="inlineStr">
         <is>
           <t>20.03</t>
         </is>
       </c>
-      <c r="E58" s="22" t="inlineStr">
+      <c r="E65" s="22" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
+      <c r="F65" s="19" t="inlineStr">
         <is>
           <t>197-17-К/26</t>
         </is>
       </c>
-      <c r="G58" s="19" t="inlineStr">
+      <c r="G65" s="19" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H58" s="23" t="inlineStr">
+      <c r="H65" s="23" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I58" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19" t="n">
+      <c r="I65" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>OPM1024_01</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>P050042</t>
         </is>
       </c>
-      <c r="D59" s="21" t="inlineStr">
+      <c r="D66" s="21" t="inlineStr">
         <is>
           <t>15.38</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E66" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>ППК25117</t>
         </is>
       </c>
-      <c r="G59" s="19" t="inlineStr">
+      <c r="G66" s="19" t="inlineStr">
         <is>
           <t>06.05.2025</t>
         </is>
       </c>
-      <c r="H59" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I59" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="32" t="n">
+      <c r="H66" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I66" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="B60" s="33" t="inlineStr">
+      <c r="B67" s="33" t="inlineStr">
         <is>
           <t>OPM1024_02</t>
         </is>
       </c>
-      <c r="C60" s="32" t="inlineStr">
+      <c r="C67" s="32" t="inlineStr">
         <is>
           <t>P050062</t>
         </is>
       </c>
-      <c r="D60" s="21" t="inlineStr">
+      <c r="D67" s="21" t="inlineStr">
         <is>
           <t>18.27</t>
         </is>
       </c>
-      <c r="E60" s="22" t="inlineStr">
+      <c r="E67" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>ППК21554</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
+      <c r="G67" s="19" t="inlineStr">
         <is>
           <t>24.06.2025</t>
         </is>
       </c>
-      <c r="H60" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I60" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="D61" s="21" t="inlineStr">
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="D68" s="21" t="inlineStr">
         <is>
           <t>18.04</t>
         </is>
       </c>
-      <c r="E61" s="22" t="inlineStr">
+      <c r="E68" s="22" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>197-18-К/26</t>
         </is>
       </c>
-      <c r="G61" s="19" t="inlineStr">
+      <c r="G68" s="19" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H61" s="23" t="inlineStr">
+      <c r="H68" s="23" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I61" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="19" t="n">
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B62" s="20" t="inlineStr">
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>OPM1024_03</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>P050082</t>
         </is>
       </c>
-      <c r="D62" s="21" t="inlineStr">
+      <c r="D69" s="21" t="inlineStr">
         <is>
           <t>16.55</t>
         </is>
       </c>
-      <c r="E62" s="22" t="inlineStr">
+      <c r="E69" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>ППК25210</t>
         </is>
       </c>
-      <c r="G62" s="19" t="inlineStr">
+      <c r="G69" s="19" t="inlineStr">
         <is>
           <t>28.07.2025</t>
         </is>
       </c>
-      <c r="H62" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I62" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="19" t="n">
+      <c r="H69" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="B63" s="20" t="inlineStr">
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>OPM052501</t>
         </is>
       </c>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>P050132</t>
         </is>
       </c>
-      <c r="D63" s="21" t="inlineStr">
+      <c r="D70" s="21" t="inlineStr">
         <is>
           <t>14.16</t>
         </is>
       </c>
-      <c r="E63" s="22" t="inlineStr">
+      <c r="E70" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>ППК52557</t>
         </is>
       </c>
-      <c r="G63" s="19" t="inlineStr">
+      <c r="G70" s="19" t="inlineStr">
         <is>
           <t>05.09.2025</t>
         </is>
       </c>
-      <c r="H63" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I63" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="19" t="n">
+      <c r="H70" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>OPM092501</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>P060042</t>
         </is>
       </c>
-      <c r="D64" s="21" t="inlineStr">
+      <c r="D71" s="21" t="inlineStr">
         <is>
           <t>9.43</t>
         </is>
       </c>
-      <c r="E64" s="22" t="inlineStr">
+      <c r="E71" s="22" t="inlineStr">
         <is>
           <t>8.48 – 10.37 %</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>ППК26008</t>
         </is>
       </c>
-      <c r="G64" s="19" t="inlineStr">
+      <c r="G71" s="19" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H64" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I64" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="19" t="n">
+      <c r="H71" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="19" t="n">
         <v>52</v>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>OPM112501</t>
         </is>
       </c>
-      <c r="C65" s="19" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>P060222</t>
         </is>
       </c>
-      <c r="D65" s="21" t="inlineStr">
+      <c r="D72" s="21" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="E65" s="22" t="inlineStr">
+      <c r="E72" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F65" s="19" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>ППК26031</t>
         </is>
       </c>
-      <c r="G65" s="19" t="inlineStr">
+      <c r="G72" s="19" t="inlineStr">
         <is>
           <t>05.03.2026</t>
         </is>
       </c>
-      <c r="H65" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I65" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="32" t="n">
+      <c r="H72" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="n">
         <v>58</v>
       </c>
-      <c r="B66" s="33" t="inlineStr">
+      <c r="B73" s="33" t="inlineStr">
         <is>
           <t>OPM122501</t>
         </is>
       </c>
-      <c r="C66" s="32" t="inlineStr">
+      <c r="C73" s="32" t="inlineStr">
         <is>
           <t>P060242</t>
         </is>
       </c>
-      <c r="D66" s="21" t="inlineStr">
+      <c r="D73" s="21" t="inlineStr">
         <is>
           <t>8.09</t>
         </is>
       </c>
-      <c r="E66" s="22" t="inlineStr">
+      <c r="E73" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>100-4-К/26</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
+      <c r="G73" s="19" t="inlineStr">
         <is>
           <t>09.04.2026</t>
         </is>
       </c>
-      <c r="H66" s="23" t="inlineStr">
+      <c r="H73" s="23" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I66" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="n"/>
-      <c r="B67" s="31" t="n"/>
-      <c r="C67" s="31" t="n"/>
-      <c r="D67" s="27" t="inlineStr">
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="n"/>
+      <c r="B74" s="31" t="n"/>
+      <c r="C74" s="31" t="n"/>
+      <c r="D74" s="27" t="inlineStr">
         <is>
           <t>7.91</t>
         </is>
       </c>
-      <c r="E67" s="28" t="inlineStr">
+      <c r="E74" s="28" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F67" s="25" t="inlineStr">
+      <c r="F74" s="25" t="inlineStr">
         <is>
           <t>197-19-К/26</t>
         </is>
       </c>
-      <c r="G67" s="25" t="inlineStr">
+      <c r="G74" s="25" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H67" s="29" t="inlineStr">
+      <c r="H74" s="29" t="inlineStr">
         <is>
           <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I67" s="30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cap Junkie      2 batch(es)      Total Δ⁹-THC across batches: 16.56 – 21.51 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>CJ062501/2</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>P050212</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>16.56</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>14.9 – 18.2 %</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>ППК25322</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>23.10.2025</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>18.91</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>197-4-К/26</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>CJ062501/1</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>P050222</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>21.51</t>
-        </is>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>n/a (informational)</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>ППК25321</t>
-        </is>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>23.10.2025</t>
-        </is>
-      </c>
-      <c r="H71" s="17" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I71" s="18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Wedding Crasher      2 batch(es)      Total Δ⁹-THC across batches: 21.67 – 22.11 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="B73" s="20" t="inlineStr">
-        <is>
-          <t>WC072501</t>
-        </is>
-      </c>
-      <c r="C73" s="19" t="inlineStr">
-        <is>
-          <t>P050262</t>
-        </is>
-      </c>
-      <c r="D73" s="21" t="inlineStr">
-        <is>
-          <t>22.11</t>
-        </is>
-      </c>
-      <c r="E73" s="22" t="inlineStr">
-        <is>
-          <t>n/a (informational)</t>
-        </is>
-      </c>
-      <c r="F73" s="19" t="inlineStr">
-        <is>
-          <t>ППК25369</t>
-        </is>
-      </c>
-      <c r="G73" s="19" t="inlineStr">
-        <is>
-          <t>28.11.2025</t>
-        </is>
-      </c>
-      <c r="H73" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I73" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="25" t="n">
-        <v>36</v>
-      </c>
-      <c r="B74" s="26" t="inlineStr">
-        <is>
-          <t>WC082501</t>
-        </is>
-      </c>
-      <c r="C74" s="25" t="inlineStr">
-        <is>
-          <t>P060012</t>
-        </is>
-      </c>
-      <c r="D74" s="27" t="inlineStr">
-        <is>
-          <t>21.67</t>
-        </is>
-      </c>
-      <c r="E74" s="28" t="inlineStr">
-        <is>
-          <t>19.5 – 23.83 %</t>
-        </is>
-      </c>
-      <c r="F74" s="25" t="inlineStr">
-        <is>
-          <t>ППК26001</t>
-        </is>
-      </c>
-      <c r="G74" s="25" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H74" s="29" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I74" s="30" t="inlineStr">
@@ -3163,398 +3226,373 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Permanent Market      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
+          <t xml:space="preserve">   Wedding Crasher      2 batch(es)      Total Δ⁹-THC across batches: 21.67 – 22.11 %</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>WC072501</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>P050262</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>22.11</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>n/a (informational)</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>ППК25369</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>WC082501</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>P060012</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>21.67</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>19.5 – 23.83 %</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>ППК26001</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Permanent Market      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B79" s="20" t="inlineStr">
         <is>
           <t>PM072501</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C79" s="19" t="inlineStr">
         <is>
           <t>P050272</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="21" t="inlineStr">
         <is>
           <t>10.01</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E79" s="22" t="inlineStr">
         <is>
           <t>9 – 11.01 %</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
+      <c r="F79" s="19" t="inlineStr">
         <is>
           <t>ППК25368</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G79" s="19" t="inlineStr">
         <is>
           <t>28.11.2025</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="H79" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="32" t="n">
         <v>41</v>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B80" s="33" t="inlineStr">
         <is>
           <t>PM092501</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C80" s="32" t="inlineStr">
         <is>
           <t>P060062</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D80" s="21" t="inlineStr">
         <is>
           <t>14.06</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E80" s="22" t="inlineStr">
         <is>
           <t>12.65 – 15.46 %</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F80" s="19" t="inlineStr">
         <is>
           <t>ППК26004</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G80" s="19" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="D78" s="7" t="inlineStr">
+      <c r="H80" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I80" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="D81" s="21" t="inlineStr">
         <is>
           <t>12.25</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E81" s="22" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
+      <c r="F81" s="19" t="inlineStr">
         <is>
           <t>197-20-К/26</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G81" s="19" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H78" s="10" t="inlineStr">
+      <c r="H81" s="23" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="13" t="n">
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="25" t="n">
         <v>53</v>
       </c>
-      <c r="B79" s="14" t="inlineStr">
+      <c r="B82" s="26" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="C79" s="13" t="inlineStr">
+      <c r="C82" s="25" t="inlineStr">
         <is>
           <t>P060232</t>
         </is>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="D82" s="27" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E82" s="28" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F79" s="13" t="inlineStr">
+      <c r="F82" s="25" t="inlineStr">
         <is>
           <t>ППК26030</t>
         </is>
       </c>
-      <c r="G79" s="13" t="inlineStr">
+      <c r="G82" s="25" t="inlineStr">
         <is>
           <t>05.03.2026</t>
         </is>
       </c>
-      <c r="H79" s="17" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I79" s="18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="H82" s="29" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I82" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Clemosa a bud      1 batch(es)      Total Δ⁹-THC across batches: 8.02 %</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="25" t="n">
+    <row r="84">
+      <c r="A84" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B81" s="26" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>CLE072501</t>
         </is>
       </c>
-      <c r="C81" s="25" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>P050282</t>
         </is>
       </c>
-      <c r="D81" s="27" t="inlineStr">
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="E81" s="28" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t>7.2 – 8.82 %</t>
         </is>
       </c>
-      <c r="F81" s="25" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>PP CoA #027 / ППК25370</t>
         </is>
       </c>
-      <c r="G81" s="25" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H81" s="29" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I81" s="30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cap Junky      3 batch(es)      Total Δ⁹-THC across batches: 18.29 – 24.96 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>CJ082501/1</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>P060022</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>24.96</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>22.46 – 27.45 %</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>ППК26002</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Apple and Banana      1 batch(es)      Total Δ⁹-THC across batches: 16.93 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
+        <is>
+          <t>AB092501</t>
+        </is>
+      </c>
+      <c r="C86" s="25" t="inlineStr">
+        <is>
+          <t>P060052</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
+        <is>
+          <t>15.23 – 18.62 %</t>
+        </is>
+      </c>
+      <c r="F86" s="25" t="inlineStr">
+        <is>
+          <t>PP CoA #037 / ППК26005</t>
+        </is>
+      </c>
+      <c r="G86" s="25" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>CJ082501/2</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>P060032</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>20.84</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>18.75 – 22.92 %</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>ППК26003</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>18.29</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>197-5-К/26</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>CJ092501</t>
-        </is>
-      </c>
-      <c r="C86" s="13" t="inlineStr">
-        <is>
-          <t>P060072</t>
-        </is>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>22.30</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>20.07 – 24.53 %</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="inlineStr">
-        <is>
-          <t>ППК26007</t>
-        </is>
-      </c>
-      <c r="G86" s="13" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H86" s="17" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I86" s="18" t="inlineStr">
+      <c r="H86" s="29" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I86" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3563,221 +3601,246 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Apple and Banana      1 batch(es)      Total Δ⁹-THC across batches: 16.93 %</t>
+          <t xml:space="preserve">   Sleepy Joy      3 batch(es)      Total Δ⁹-THC across batches: 9.20 – 11.20 %</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="B88" s="26" t="inlineStr">
-        <is>
-          <t>AB092501</t>
-        </is>
-      </c>
-      <c r="C88" s="25" t="inlineStr">
-        <is>
-          <t>P060052</t>
-        </is>
-      </c>
-      <c r="D88" s="27" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="E88" s="28" t="inlineStr">
-        <is>
-          <t>15.23 – 18.62 %</t>
-        </is>
-      </c>
-      <c r="F88" s="25" t="inlineStr">
-        <is>
-          <t>PP CoA #037 / ППК26005</t>
-        </is>
-      </c>
-      <c r="G88" s="25" t="inlineStr">
+      <c r="A88" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>SJ092501</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>P060082</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>10.96</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>9.86 – 12.05 %</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>ППК26006</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H88" s="29" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I88" s="30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Sleepy Joy      3 batch(es)      Total Δ⁹-THC across batches: 9.20 – 11.20 %</t>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>SJ102501</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>P060162</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>11.20</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>051-3-K/26</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>SJ092501</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>P060082</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t>9.86 – 12.05 %</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>ППК26006</t>
-        </is>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>SJ102501</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>P060162</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>11.20</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="A90" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>SJ112501</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>P060192</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>9.20</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>051-3-K/26</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>051-2-K/26</t>
+        </is>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
         <is>
           <t>04.03.2026</t>
         </is>
       </c>
-      <c r="H91" s="10" t="inlineStr">
+      <c r="H90" s="17" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I91" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Jokerz 31      3 batch(es)      Total Δ⁹-THC across batches: 17.32 – 25.27 %</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="13" t="n">
-        <v>49</v>
-      </c>
-      <c r="B92" s="14" t="inlineStr">
-        <is>
-          <t>SJ112501</t>
-        </is>
-      </c>
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>P060192</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>9.20</t>
-        </is>
-      </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="A92" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="B92" s="33" t="inlineStr">
+        <is>
+          <t>J31102501</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>P060152</t>
+        </is>
+      </c>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F92" s="13" t="inlineStr">
-        <is>
-          <t>051-2-K/26</t>
-        </is>
-      </c>
-      <c r="G92" s="13" t="inlineStr">
+      <c r="F92" s="19" t="inlineStr">
+        <is>
+          <t>051-1-K/26</t>
+        </is>
+      </c>
+      <c r="G92" s="19" t="inlineStr">
         <is>
           <t>04.03.2026</t>
         </is>
       </c>
-      <c r="H92" s="17" t="inlineStr">
+      <c r="H92" s="23" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I92" s="18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Jokerz 31      3 batch(es)      Total Δ⁹-THC across batches: 17.32 – 25.27 %</t>
+      <c r="I92" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>17.32</t>
+        </is>
+      </c>
+      <c r="E93" s="22" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F93" s="19" t="inlineStr">
+        <is>
+          <t>197-16-К/26</t>
+        </is>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="32" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B94" s="33" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
         <is>
-          <t>P060152</t>
+          <t>P060202</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="E94" s="22" t="inlineStr">
@@ -3787,7 +3850,7 @@
       </c>
       <c r="F94" s="19" t="inlineStr">
         <is>
-          <t>051-1-K/26</t>
+          <t>051-5-K/26</t>
         </is>
       </c>
       <c r="G94" s="19" t="inlineStr">
@@ -3809,22 +3872,22 @@
     <row r="95">
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="E95" s="22" t="inlineStr">
         <is>
-          <t>≥ 5.00 %</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F95" s="19" t="inlineStr">
         <is>
-          <t>197-16-К/26</t>
+          <t>100-1-K/26</t>
         </is>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H95" s="23" t="inlineStr">
@@ -3840,21 +3903,21 @@
     </row>
     <row r="96">
       <c r="A96" s="32" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B96" s="33" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
         <is>
-          <t>P060202</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="E96" s="22" t="inlineStr">
@@ -3864,132 +3927,107 @@
       </c>
       <c r="F96" s="19" t="inlineStr">
         <is>
-          <t>051-5-K/26</t>
+          <t>100-2-К/26</t>
         </is>
       </c>
       <c r="G96" s="19" t="inlineStr">
         <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H96" s="23" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I96" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="31" t="n"/>
+      <c r="B97" s="31" t="n"/>
+      <c r="C97" s="31" t="n"/>
+      <c r="D97" s="27" t="inlineStr">
+        <is>
+          <t>21.84</t>
+        </is>
+      </c>
+      <c r="E97" s="28" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F97" s="25" t="inlineStr">
+        <is>
+          <t>100-3-К/26</t>
+        </is>
+      </c>
+      <c r="G97" s="25" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H97" s="29" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I97" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Kush Crasher      1 batch(es)      Total Δ⁹-THC across batches: 17.04 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>KC102501</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>P060172</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>17.04</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>051-4-K/26</t>
+        </is>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
           <t>04.03.2026</t>
         </is>
       </c>
-      <c r="H96" s="23" t="inlineStr">
+      <c r="H99" s="17" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I96" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="D97" s="21" t="inlineStr">
-        <is>
-          <t>20.21</t>
-        </is>
-      </c>
-      <c r="E97" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F97" s="19" t="inlineStr">
-        <is>
-          <t>100-1-K/26</t>
-        </is>
-      </c>
-      <c r="G97" s="19" t="inlineStr">
-        <is>
-          <t>09.04.2026</t>
-        </is>
-      </c>
-      <c r="H97" s="23" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I97" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="32" t="n">
-        <v>59</v>
-      </c>
-      <c r="B98" s="33" t="inlineStr">
-        <is>
-          <t>J31122501</t>
-        </is>
-      </c>
-      <c r="C98" s="32" t="inlineStr">
-        <is>
-          <t>P060262</t>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>19.84</t>
-        </is>
-      </c>
-      <c r="E98" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F98" s="19" t="inlineStr">
-        <is>
-          <t>100-2-К/26</t>
-        </is>
-      </c>
-      <c r="G98" s="19" t="inlineStr">
-        <is>
-          <t>09.04.2026</t>
-        </is>
-      </c>
-      <c r="H98" s="23" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I98" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="31" t="n"/>
-      <c r="B99" s="31" t="n"/>
-      <c r="C99" s="31" t="n"/>
-      <c r="D99" s="27" t="inlineStr">
-        <is>
-          <t>21.84</t>
-        </is>
-      </c>
-      <c r="E99" s="28" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F99" s="25" t="inlineStr">
-        <is>
-          <t>100-3-К/26</t>
-        </is>
-      </c>
-      <c r="G99" s="25" t="inlineStr">
-        <is>
-          <t>09.04.2026</t>
-        </is>
-      </c>
-      <c r="H99" s="29" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I99" s="30" t="inlineStr">
+      <c r="I99" s="18" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3998,50 +4036,50 @@
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Kush Crasher      1 batch(es)      Total Δ⁹-THC across batches: 17.04 %</t>
+          <t xml:space="preserve">   Graps &amp; Creme      1 batch(es)      Total Δ⁹-THC across batches: 11.53 %</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="13" t="n">
-        <v>47</v>
-      </c>
-      <c r="B101" s="14" t="inlineStr">
-        <is>
-          <t>KC102501</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>P060172</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="E101" s="16" t="inlineStr">
+      <c r="A101" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="B101" s="26" t="inlineStr">
+        <is>
+          <t>GRC102501/2</t>
+        </is>
+      </c>
+      <c r="C101" s="25" t="inlineStr">
+        <is>
+          <t>P060182</t>
+        </is>
+      </c>
+      <c r="D101" s="27" t="inlineStr">
+        <is>
+          <t>11.53</t>
+        </is>
+      </c>
+      <c r="E101" s="28" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F101" s="13" t="inlineStr">
-        <is>
-          <t>051-4-K/26</t>
-        </is>
-      </c>
-      <c r="G101" s="13" t="inlineStr">
+      <c r="F101" s="25" t="inlineStr">
+        <is>
+          <t>051-6-K/26</t>
+        </is>
+      </c>
+      <c r="G101" s="25" t="inlineStr">
         <is>
           <t>04.03.2026</t>
         </is>
       </c>
-      <c r="H101" s="17" t="inlineStr">
+      <c r="H101" s="29" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I101" s="18" t="inlineStr">
+      <c r="I101" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4050,97 +4088,105 @@
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Graps &amp; Creme      1 batch(es)      Total Δ⁹-THC across batches: 11.53 %</t>
+          <t xml:space="preserve">   Jelly Donutz      5 batch(es)      Total Δ⁹-THC across batches: 13.93 – 20.54 %</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="25" t="n">
-        <v>48</v>
-      </c>
-      <c r="B103" s="26" t="inlineStr">
-        <is>
-          <t>GRC102501/2</t>
-        </is>
-      </c>
-      <c r="C103" s="25" t="inlineStr">
-        <is>
-          <t>P060182</t>
-        </is>
-      </c>
-      <c r="D103" s="27" t="inlineStr">
-        <is>
-          <t>11.53</t>
-        </is>
-      </c>
-      <c r="E103" s="28" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F103" s="25" t="inlineStr">
-        <is>
-          <t>051-6-K/26</t>
-        </is>
-      </c>
-      <c r="G103" s="25" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="H103" s="29" t="inlineStr">
+      <c r="A103" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>JD112501</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>19.64</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr"/>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>ППК26063</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>13.93</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr"/>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>ППК26065</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>20.32</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>197-15-К/26</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I103" s="30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Jelly Donutz      5 batch(es)      Total Δ⁹-THC across batches: 13.93 – 20.54 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>JD112501</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>P060212</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr"/>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>ППК26063</t>
-        </is>
-      </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H105" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
           <t>Open</t>
@@ -4148,15 +4194,28 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>JD012601</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr"/>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>ППК26065</t>
+          <t>ППК26064</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
@@ -4176,9 +4235,22 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>JD012603/2</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -4188,17 +4260,17 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>197-15-К/26</t>
+          <t>ППК26113</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
@@ -4209,433 +4281,429 @@
     </row>
     <row r="108">
       <c r="A108" s="9" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>JD012601</t>
+          <t>JD012603/2V</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>P060312</t>
+          <t>P060422</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>18.16</t>
-        </is>
-      </c>
-      <c r="E108" s="8" t="inlineStr"/>
+          <t>15.16</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>ППК26064</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>JD022601</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr"/>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>18.58</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>ППК26115</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="H109" s="17" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Cash Cow      2 batch(es)      Total Δ⁹-THC across batches: 13.35 – 17.67 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="B111" s="20" t="inlineStr">
+        <is>
+          <t>CC112501</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>P060272</t>
+        </is>
+      </c>
+      <c r="D111" s="21" t="inlineStr">
+        <is>
+          <t>13.35</t>
+        </is>
+      </c>
+      <c r="E111" s="22" t="inlineStr"/>
+      <c r="F111" s="19" t="inlineStr">
+        <is>
+          <t>ППК26068</t>
+        </is>
+      </c>
+      <c r="G111" s="19" t="inlineStr">
+        <is>
           <t>11.05.2026</t>
         </is>
       </c>
-      <c r="H108" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I108" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>JD012603/2</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>P060412</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>20.54</t>
-        </is>
-      </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I111" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B112" s="26" t="inlineStr">
+        <is>
+          <t>CC012601/1</t>
+        </is>
+      </c>
+      <c r="C112" s="25" t="inlineStr">
+        <is>
+          <t>P060332</t>
+        </is>
+      </c>
+      <c r="D112" s="27" t="inlineStr">
+        <is>
+          <t>17.67</t>
+        </is>
+      </c>
+      <c r="E112" s="28" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>ППК26113</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
+      <c r="F112" s="25" t="inlineStr">
+        <is>
+          <t>197-6-К/26</t>
+        </is>
+      </c>
+      <c r="G112" s="25" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H112" s="29" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I112" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Scrambler      3 batch(es)      Total Δ⁹-THC across batches: 17.13 – 21.92 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>P060282</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>17.13</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr"/>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>ППК26069</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>SCR012603</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>17.84</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>197-21-К/26</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>SCR022601</t>
+        </is>
+      </c>
+      <c r="C116" s="13" t="inlineStr"/>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>21.92</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="inlineStr">
+        <is>
+          <t>ППК26116</t>
+        </is>
+      </c>
+      <c r="G116" s="13" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fat Bastard      6 batch(es)      Total Δ⁹-THC across batches: 12.39 – 20.83 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>FB112501</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="inlineStr">
+        <is>
+          <t>P060292</t>
+        </is>
+      </c>
+      <c r="D118" s="21" t="inlineStr">
+        <is>
+          <t>16.69</t>
+        </is>
+      </c>
+      <c r="E118" s="22" t="inlineStr"/>
+      <c r="F118" s="19" t="inlineStr">
+        <is>
+          <t>ППК26066</t>
+        </is>
+      </c>
+      <c r="G118" s="19" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H118" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I118" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>FB012603</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr"/>
+      <c r="D119" s="21" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
+      </c>
+      <c r="E119" s="22" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
+      <c r="F119" s="19" t="inlineStr">
+        <is>
+          <t>ППК26112</t>
+        </is>
+      </c>
+      <c r="G119" s="19" t="inlineStr">
         <is>
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="H109" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I109" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="B110" s="12" t="inlineStr">
-        <is>
-          <t>JD012603/2V</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>P060422</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>ППК26111</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I110" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="13" t="n">
-        <v>71</v>
-      </c>
-      <c r="B111" s="14" t="inlineStr">
-        <is>
-          <t>JD022601</t>
-        </is>
-      </c>
-      <c r="C111" s="13" t="inlineStr"/>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>18.58</t>
-        </is>
-      </c>
-      <c r="E111" s="16" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F111" s="13" t="inlineStr">
-        <is>
-          <t>ППК26115</t>
-        </is>
-      </c>
-      <c r="G111" s="13" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H111" s="17" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I111" s="18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cash Cow      2 batch(es)      Total Δ⁹-THC across batches: 13.35 – 17.67 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="19" t="n">
-        <v>55</v>
-      </c>
-      <c r="B113" s="20" t="inlineStr">
-        <is>
-          <t>CC112501</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>P060272</t>
-        </is>
-      </c>
-      <c r="D113" s="21" t="inlineStr">
-        <is>
-          <t>13.35</t>
-        </is>
-      </c>
-      <c r="E113" s="22" t="inlineStr"/>
-      <c r="F113" s="19" t="inlineStr">
-        <is>
-          <t>ППК26068</t>
-        </is>
-      </c>
-      <c r="G113" s="19" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H113" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I113" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="25" t="n">
-        <v>64</v>
-      </c>
-      <c r="B114" s="26" t="inlineStr">
-        <is>
-          <t>CC012601/1</t>
-        </is>
-      </c>
-      <c r="C114" s="25" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
-      <c r="D114" s="27" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
-      </c>
-      <c r="E114" s="28" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F114" s="25" t="inlineStr">
-        <is>
-          <t>197-6-К/26</t>
-        </is>
-      </c>
-      <c r="G114" s="25" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H114" s="29" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I114" s="30" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Scrambler      3 batch(es)      Total Δ⁹-THC across batches: 17.13 – 21.92 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t>SCR112501</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>P060282</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr"/>
-      <c r="F116" s="9" t="inlineStr">
-        <is>
-          <t>ППК26069</t>
-        </is>
-      </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I116" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t>SCR012603</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>P060382</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr">
-        <is>
-          <t>197-21-К/26</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I117" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="13" t="n">
-        <v>72</v>
-      </c>
-      <c r="B118" s="14" t="inlineStr">
-        <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="C118" s="13" t="inlineStr"/>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
-      </c>
-      <c r="E118" s="16" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F118" s="13" t="inlineStr">
-        <is>
-          <t>ППК26116</t>
-        </is>
-      </c>
-      <c r="G118" s="13" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="H118" s="17" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I118" s="18" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Fat Bastard      6 batch(es)      Total Δ⁹-THC across batches: 12.39 – 20.83 %</t>
+      <c r="H119" s="23" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I119" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="19" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>FB012601/1</t>
         </is>
       </c>
       <c r="C120" s="19" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060322</t>
         </is>
       </c>
       <c r="D120" s="21" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="E120" s="22" t="inlineStr"/>
       <c r="F120" s="19" t="inlineStr">
         <is>
-          <t>ППК26066</t>
+          <t>ППК26067</t>
         </is>
       </c>
       <c r="G120" s="19" t="inlineStr">
@@ -4656,17 +4724,21 @@
     </row>
     <row r="121">
       <c r="A121" s="19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>FB012603</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr"/>
+          <t>FB012602</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
       <c r="D121" s="21" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="E121" s="22" t="inlineStr">
@@ -4676,17 +4748,17 @@
       </c>
       <c r="F121" s="19" t="inlineStr">
         <is>
-          <t>ППК26112</t>
+          <t>197-7-К/26</t>
         </is>
       </c>
       <c r="G121" s="19" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H121" s="23" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I121" s="24" t="inlineStr">
@@ -4697,32 +4769,36 @@
     </row>
     <row r="122">
       <c r="A122" s="19" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>FB012601/1</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="C122" s="19" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060392</t>
         </is>
       </c>
       <c r="D122" s="21" t="inlineStr">
         <is>
-          <t>14.68</t>
-        </is>
-      </c>
-      <c r="E122" s="22" t="inlineStr"/>
+          <t>18.29</t>
+        </is>
+      </c>
+      <c r="E122" s="22" t="inlineStr">
+        <is>
+          <t>≥ 5.00 %</t>
+        </is>
+      </c>
       <c r="F122" s="19" t="inlineStr">
         <is>
-          <t>ППК26067</t>
+          <t>ППК26110</t>
         </is>
       </c>
       <c r="G122" s="19" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H122" s="23" t="inlineStr">
@@ -4737,221 +4813,129 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="19" t="n">
-        <v>65</v>
-      </c>
-      <c r="B123" s="20" t="inlineStr">
-        <is>
-          <t>FB012602</t>
-        </is>
-      </c>
-      <c r="C123" s="19" t="inlineStr">
-        <is>
-          <t>P060352</t>
-        </is>
-      </c>
-      <c r="D123" s="21" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="E123" s="22" t="inlineStr">
+      <c r="A123" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="B123" s="26" t="inlineStr">
+        <is>
+          <t>FB032601</t>
+        </is>
+      </c>
+      <c r="C123" s="25" t="inlineStr"/>
+      <c r="D123" s="27" t="inlineStr">
+        <is>
+          <t>12.39</t>
+        </is>
+      </c>
+      <c r="E123" s="28" t="inlineStr">
         <is>
           <t>≥ 5.00 %</t>
         </is>
       </c>
-      <c r="F123" s="19" t="inlineStr">
-        <is>
-          <t>197-7-К/26</t>
-        </is>
-      </c>
-      <c r="G123" s="19" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H123" s="23" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I123" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="19" t="n">
-        <v>67</v>
-      </c>
-      <c r="B124" s="20" t="inlineStr">
-        <is>
-          <t>FB012603V</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="inlineStr">
-        <is>
-          <t>P060392</t>
-        </is>
-      </c>
-      <c r="D124" s="21" t="inlineStr">
-        <is>
-          <t>18.29</t>
-        </is>
-      </c>
-      <c r="E124" s="22" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F124" s="19" t="inlineStr">
-        <is>
-          <t>ППК26110</t>
-        </is>
-      </c>
-      <c r="G124" s="19" t="inlineStr">
-        <is>
-          <t>30.06.2026</t>
-        </is>
-      </c>
-      <c r="H124" s="23" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I124" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="25" t="n">
-        <v>73</v>
-      </c>
-      <c r="B125" s="26" t="inlineStr">
-        <is>
-          <t>FB032601</t>
-        </is>
-      </c>
-      <c r="C125" s="25" t="inlineStr"/>
-      <c r="D125" s="27" t="inlineStr">
-        <is>
-          <t>12.39</t>
-        </is>
-      </c>
-      <c r="E125" s="28" t="inlineStr">
-        <is>
-          <t>≥ 5.00 %</t>
-        </is>
-      </c>
-      <c r="F125" s="25" t="inlineStr">
+      <c r="F123" s="25" t="inlineStr">
         <is>
           <t>ППК26127</t>
         </is>
       </c>
-      <c r="G125" s="25" t="inlineStr">
+      <c r="G123" s="25" t="inlineStr">
         <is>
           <t>21.07.2026</t>
         </is>
       </c>
-      <c r="H125" s="29" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy</t>
-        </is>
-      </c>
-      <c r="I125" s="30" t="inlineStr">
+      <c r="H123" s="29" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="I123" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I125"/>
-  <mergeCells count="82">
+  <autoFilter ref="A4:I123"/>
+  <mergeCells count="80">
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A56:I56"/>
     <mergeCell ref="C94:C95"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A117:I117"/>
     <mergeCell ref="C27:C28"/>
-    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B64:B65"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="B54:B55"/>
     <mergeCell ref="A87:I87"/>
-    <mergeCell ref="C98:C99"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A89:I89"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B77:B78"/>
     <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B58:B59"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="B67:B68"/>
     <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="A91:I91"/>
     <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A63:I63"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A115:I115"/>
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="C17:C18"/>
-    <mergeCell ref="A93:I93"/>
     <mergeCell ref="A102:I102"/>
     <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="B92:B93"/>
     <mergeCell ref="B30:B31"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A105:A107"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A39:A40"/>
     <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A78:I78"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="C73:C74"/>
     <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A36:A37"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A104:I104"/>
-    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="A113:I113"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B98:B99"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B105:B107"/>
     <mergeCell ref="B36:B37"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="A119:I119"/>
-    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="A110:I110"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A67:A68"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C105:C107"/>
-    <mergeCell ref="B47:B48"/>
     <mergeCell ref="B96:B97"/>
     <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="A47:I47"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A72:I72"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A112:I112"/>
-    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="C67:C68"/>
     <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A103:A105"/>
+    <mergeCell ref="C103:C105"/>
     <mergeCell ref="C96:C97"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B50:B51"/>
     <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C92:C93"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
@@ -4984,75 +4968,75 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_THC_by_Strain.xlsx
@@ -3323,7 +3323,7 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Permanent Market      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
+          <t xml:space="preserve">   Permanent Marker      3 batch(es)      Total Δ⁹-THC across batches: 10.01 – 14.06 %</t>
         </is>
       </c>
     </row>
